--- a/data/trans_dic/IP31KM14_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM14_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,79; 24,99</t>
+          <t>11,33; 25,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,63; 31,47</t>
+          <t>12,35; 26,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,56; 25,17</t>
+          <t>12,96; 22,58</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,04; 21,61</t>
+          <t>13,65; 23,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,82; 23,09</t>
+          <t>12,13; 20,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,75; 20,64</t>
+          <t>14,14; 20,89</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 18,49</t>
+          <t>15,04; 26,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,18; 25,09</t>
+          <t>9,59; 18,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,62; 20,13</t>
+          <t>13,18; 20,38</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,41%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>24,88%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19,84%</t>
-        </is>
-      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,34; 31,03</t>
+          <t>14,28; 24,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 25,92</t>
+          <t>19,57; 30,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,34; 26,75</t>
+          <t>18,5; 25,99</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 20,53</t>
+          <t>16,12; 21,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,24; 22,69</t>
+          <t>15,42; 20,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,22; 20,61</t>
+          <t>16,48; 20,37</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19586</t>
+          <t>20767</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26633</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46220</t>
+          <t>42213</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13474; 28550</t>
+          <t>13923; 30750</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17283; 43050</t>
+          <t>14644; 31023</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34039; 63187</t>
+          <t>31286; 54530</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>30477</t>
+          <t>41819</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>43455</t>
+          <t>29118</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73932</t>
+          <t>70936</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22402; 40222</t>
+          <t>31565; 54632</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34214; 57153</t>
+          <t>21913; 37608</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59611; 89482</t>
+          <t>58216; 86014</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23190</t>
+          <t>33023</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35950</t>
+          <t>20826</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59140</t>
+          <t>53848</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13597; 34800</t>
+          <t>25048; 44107</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25962; 45940</t>
+          <t>14864; 29157</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43137; 74744</t>
+          <t>42371; 65550</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>40927</t>
+          <t>32247</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>35172</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76099</t>
+          <t>73053</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31819; 51043</t>
+          <t>23730; 41437</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25590; 45962</t>
+          <t>32083; 50563</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62676; 91440</t>
+          <t>61069; 85815</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>157</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>114180</t>
+          <t>127855</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>141210</t>
+          <t>112195</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>255390</t>
+          <t>240050</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>94435; 134058</t>
+          <t>110698; 148862</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>120956; 168997</t>
+          <t>95356; 129370</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>226784; 288156</t>
+          <t>215056; 265890</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM14_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM14_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que desayunan bollería industrial (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>16,9%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>11,33; 25,02</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12,35; 26,16</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12,96; 22,58</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>13,65; 23,63</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12,13; 20,82</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14,14; 20,89</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>19,83%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>13,43%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>15,04; 26,49</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9,59; 18,81</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>13,18; 20,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>24,88%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>14,28; 24,94</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>19,57; 30,84</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18,5; 25,99</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>18,62%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>18,15%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>16,12; 21,67</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15,42; 20,93</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16,48; 20,37</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.1689813343922578</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1808254701088765</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1747979876851465</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>20767</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>21446</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42213</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.1132892990071577</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1234736722274523</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1295501077082858</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>13923; 30750</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>14644; 31023</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>31286; 54530</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.2502104920665926</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.2615775325098726</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.2258043999028259</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1808450660992008</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1612335357568649</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1722452248135521</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>41819</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>29118</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>70936</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1365033666067169</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1213399523285769</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1413585744138917</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>31565; 54632</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>21913; 37608</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>58216; 86014</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.2362552175145396</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.2082490823036527</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.2088576892111522</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1983083863556667</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1343259268475014</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1674596347791691</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>33023</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>20826</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53848</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1504156100615785</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.09587034705240068</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.131765901638217</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>25048; 44107</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>14864; 29157</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>42371; 65550</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2648707554244781</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1880636488398668</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.2038489758663674</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1940633176888526</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.2488498039735036</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.2212751825553749</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>32247</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>40806</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>73053</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1428093808158812</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1956549992204467</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1849764342621635</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>23730; 41437</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>32083; 50563</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>61069; 85815</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.2493704381240873</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.3083529778588672</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2599331955771155</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1861541793670633</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.181484130594831</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1839419260049512</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>127855</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>112195</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>240050</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1611731664784765</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1542460378430545</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.1647899339923755</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>110698; 148862</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>95356; 129370</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>215056; 265890</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.216740078192304</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.209266430634316</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.2037425103976177</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que desayunan bollería industrial (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>20767</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>21446</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>42213</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>13923</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>14644</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>31286</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>30750</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>31023</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>54530</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>41819</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>29118</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>70936</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>31565</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>21913</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>58216</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>54632</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>37608</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>86014</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>33023</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>20826</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>53848</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>25048</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>14864</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>42371</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>44107</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>29157</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>65550</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>32247</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>40806</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>73053</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>23730</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>32083</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>61069</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>41437</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>50563</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>85815</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>167</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>157</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>127855</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>112195</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>240050</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>110698</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>95356</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>215056</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>148862</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>129370</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>265890</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>